--- a/FinanceDataMigration/src/main/resources/migration-templates/BANK_BRANCH.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/BANK_BRANCH.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">Bank Branch</t>
   </si>
@@ -191,9 +191,6 @@
   <si>
     <t xml:space="preserve">Property tax collection branch</t>
   </si>
-  <si>
-    <t xml:space="preserve">Allahabad Bank</t>
-  </si>
 </sst>
 </file>
 
@@ -208,29 +205,27 @@
     </font>
     <font>
       <b/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FFC9211E"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -273,22 +268,22 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -993,9 +988,7 @@
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -1477,44 +1470,12 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <dataValidations count="3" disablePrompts="0">
-    <dataValidation sqref="B4:B44" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="C4:C44" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Bank!$C$4:$C$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="D8" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-      <formula1>Bank!$C$4:$C$9</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3" disablePrompts="0">
-        <x14:dataValidation xr:uid="{74A776A4-DBE7-4737-8E85-3E111F785535}" type="custom" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>COUNTIF($G$4:$G$44,G4)=1</xm:f>
-          </x14:formula1>
-          <xm:sqref>G4:G44</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{EB3AF984-CDEA-4F88-82C7-B543C47D250A}" type="custom" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>COUNTIF($E$4:$E$44,E4)=1</xm:f>
-          </x14:formula1>
-          <xm:sqref>E4:E44</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation xr:uid="{7757AD20-84AA-4684-84E7-6D1BA88D69FC}" type="custom" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>COUNTIF($F$4:$F$44,F4)=1</xm:f>
-          </x14:formula1>
-          <xm:sqref>F4:F44</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>